--- a/cds_files/Kansas_CDS_2022-2023.xlsx
+++ b/cds_files/Kansas_CDS_2022-2023.xlsx
@@ -496,10 +496,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8</v>
+        <v>0.25</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="4">
@@ -509,10 +509,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2</v>
+        <v>0.75</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="5">
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.77</v>
+        <v>0.771</v>
       </c>
     </row>
   </sheetData>
